--- a/Result/profitability/3321.xlsx
+++ b/Result/profitability/3321.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM58"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.65</v>
+        <v>-0.54375</v>
       </c>
       <c r="N2" t="n">
-        <v>5.202500000000001</v>
+        <v>7.0425</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-1.89</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.76875</v>
+        <v>-0.74</v>
       </c>
       <c r="N3" t="n">
-        <v>5.26125</v>
+        <v>6.5025</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-2.03</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9824999999999999</v>
+        <v>-0.90625</v>
       </c>
       <c r="N4" t="n">
-        <v>2.397500000000001</v>
+        <v>3.818750000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-5.44</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.575</v>
+        <v>-1.4525</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.203749999999999</v>
+        <v>-0.2687499999999994</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.51625</v>
+        <v>-1.50625</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.546249999999999</v>
+        <v>-1.18625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.65</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.57625</v>
+        <v>-1.48</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.754999999999999</v>
+        <v>-0.9599999999999995</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -7794,6 +7794,133 @@
       </c>
       <c r="AM58" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>692</v>
+      </c>
+      <c r="D59" t="n">
+        <v>604</v>
+      </c>
+      <c r="E59" t="n">
+        <v>89</v>
+      </c>
+      <c r="F59" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-0.605</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4.835</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X59" t="n">
+        <v>-0.8695652173913043</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>6.630952380952381</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>-0.9158878504672897</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.400749063670412</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
